--- a/results/Int Task Remove ACC -0.8/Rando_fi_explain.xlsx
+++ b/results/Int Task Remove ACC -0.8/Rando_fi_explain.xlsx
@@ -1148,268 +1148,268 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.001197231516918485</v>
+        <v>-0.001716491723528859</v>
       </c>
       <c r="C3" t="n">
         <v>0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.000323214616362969</v>
+        <v>-0.0004458126519162244</v>
       </c>
       <c r="E3" t="n">
-        <v>5.92761190055747e-05</v>
+        <v>0.001229413413362106</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0005644212192931319</v>
+        <v>0.001687709639871273</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.001805391188532531</v>
+        <v>-0.0007724884913987518</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0005574867639152479</v>
+        <v>-2.121383111622875e-06</v>
       </c>
       <c r="I3" t="n">
-        <v>4.055153151266686e-06</v>
+        <v>0.0001590313962864565</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.000953582643636657</v>
+        <v>-0.0007501602782721507</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01453746192687995</v>
+        <v>0.01396527681792127</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02025203431786942</v>
+        <v>0.01440517803275121</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.002879923393992758</v>
+        <v>-0.0008441558528720506</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.000840491437173968</v>
+        <v>-0.0003066189635860006</v>
       </c>
       <c r="O3" t="n">
-        <v>0.003885752397629712</v>
+        <v>0.003975896266473058</v>
       </c>
       <c r="P3" t="n">
-        <v>0.005524048483912551</v>
+        <v>0.003292697467800863</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.009882013187473181</v>
+        <v>0.009683025534159149</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.001936198793495702</v>
+        <v>-0.0003391068933756304</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.001278644307761019</v>
+        <v>0.0002215170553056156</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0007057003450497134</v>
+        <v>-0.001181370500362369</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.00151368647212881</v>
+        <v>-0.001032618149056563</v>
       </c>
       <c r="V3" t="n">
-        <v>-5.586270518984857e-05</v>
+        <v>-3.885397219064668e-05</v>
       </c>
       <c r="W3" t="n">
-        <v>0.002220588685504292</v>
+        <v>0.001486976070766455</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.001018244647886115</v>
+        <v>-0.001696771199963918</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.001914657998121424</v>
+        <v>0.0006590893098306417</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.000893729357740769</v>
+        <v>0.001498592186379907</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.0008927284229085341</v>
+        <v>0.00228868491372725</v>
       </c>
       <c r="AB3" t="n">
-        <v>9.730695376075399e-05</v>
+        <v>0.0002015660006151176</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.004189402012713068</v>
+        <v>0.005250161257267042</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.005364058276130997</v>
+        <v>-0.002011412658585842</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.003909738105106689</v>
+        <v>-0.001272973340499677</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.003147348077708614</v>
+        <v>-0.002629211806517788</v>
       </c>
       <c r="AG3" t="n">
-        <v>-8.659870381505954e-05</v>
+        <v>-5.415728990352916e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>-4.945454285128379e-05</v>
+        <v>0.0001484680307498853</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.004166724163500478</v>
+        <v>-0.001561257046859213</v>
       </c>
       <c r="AK3" t="n">
-        <v>-0.003468000117389192</v>
+        <v>-0.002775589784020784</v>
       </c>
       <c r="AL3" t="n">
-        <v>4.593087527056891e-05</v>
+        <v>0.0004522955240616855</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.0002717005320726596</v>
+        <v>0.0003628517452537605</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.002663550210733191</v>
+        <v>0.0007395784852407627</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.001701304495404514</v>
+        <v>-0.001525313218280108</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0003589911517067668</v>
+        <v>-0.0004317790919582431</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.001149775327152772</v>
+        <v>0.001358650285592504</v>
       </c>
       <c r="AR3" t="n">
-        <v>-0.001994183588264525</v>
+        <v>-0.004227081057436011</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.001528984685571375</v>
+        <v>0.001703546873797612</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.001054659476934011</v>
+        <v>-0.004533816070735833</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.002418909475602129</v>
+        <v>0.004442733567668299</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0003109625926731995</v>
+        <v>5.756175671968195e-06</v>
       </c>
       <c r="AW3" t="n">
-        <v>4.352967309210523e-05</v>
+        <v>-0.001081432854938724</v>
       </c>
       <c r="AX3" t="n">
-        <v>6.639154533607302e-05</v>
+        <v>5.706122808916358e-05</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.0009916901603714257</v>
+        <v>-9.839334572186328e-05</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.001019437318261283</v>
+        <v>0.000650893548632636</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0.003332006741818252</v>
+        <v>-0.00232521282713462</v>
       </c>
       <c r="BB3" t="n">
-        <v>-0.001955361737030383</v>
+        <v>-0.0006567772933850325</v>
       </c>
       <c r="BC3" t="n">
-        <v>-0.0005753555172242209</v>
+        <v>1.765943633348383e-06</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0003273115651496694</v>
+        <v>-2.624772524170701e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>-0.0004035346370283544</v>
+        <v>8.25247180671884e-05</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.002195638831528786</v>
+        <v>-0.001064896467251933</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.001369487594345415</v>
+        <v>0.001421518878046412</v>
       </c>
       <c r="BH3" t="n">
-        <v>2.717566154775169e-08</v>
+        <v>5.92066311426942e-06</v>
       </c>
       <c r="BI3" t="n">
-        <v>-5.562029125062436e-06</v>
+        <v>-0.0003779135426616409</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.001143626973610263</v>
+        <v>-0.0002719421754279951</v>
       </c>
       <c r="BK3" t="n">
-        <v>-0.002480049781243588</v>
+        <v>-0.0004474094484768987</v>
       </c>
       <c r="BL3" t="n">
-        <v>-6.678532965349929e-05</v>
+        <v>9.398092690401259e-05</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.001083068562023074</v>
+        <v>0.001006181857695863</v>
       </c>
       <c r="BN3" t="n">
-        <v>-0.003290226286123681</v>
+        <v>-0.003996186741260089</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0.001453438153237243</v>
+        <v>0.003126676780383393</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0005237983167424888</v>
+        <v>0.001782615219825001</v>
       </c>
       <c r="BQ3" t="n">
-        <v>-6.699908816333644e-05</v>
+        <v>-3.907405964517108e-05</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.0001321203455227527</v>
+        <v>0.0001986690259785129</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.0009394718890762332</v>
+        <v>-0.000305675649838647</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0004935971811712736</v>
+        <v>-0.0004104679915632481</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.002913220480064357</v>
+        <v>0.005621052254869157</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.0003128091593988947</v>
+        <v>2.904143641866306e-05</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.002235890600936076</v>
+        <v>0.003711031635426148</v>
       </c>
       <c r="BX3" t="n">
-        <v>-9.333583178565586e-05</v>
+        <v>6.496591095381142e-05</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.0003231683588154622</v>
+        <v>0.0005211712381329291</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.0001295210623701815</v>
+        <v>0.0002610289250037468</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.056234718825657e-06</v>
+        <v>-2.561668715675092e-05</v>
       </c>
       <c r="CB3" t="n">
-        <v>9.342280683560244e-05</v>
+        <v>0.0008769949750788009</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0007231842594634808</v>
+        <v>0.002882775608766825</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0004476237310102616</v>
+        <v>-0.0001295473118029433</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.0002746246983864642</v>
+        <v>0.0001625088579970191</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0007841569087743562</v>
+        <v>0.002566910684427303</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.001576993965877981</v>
+        <v>0.001553273488430857</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0004993117587286179</v>
+        <v>1.375536792571075e-05</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.001201133272803104</v>
+        <v>0.001626912970867159</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0009183362969631794</v>
+        <v>0.001501424618425418</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0002684549738231823</v>
+        <v>0.0002359000793180011</v>
       </c>
     </row>
     <row r="4">
@@ -1419,268 +1419,268 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.003862996804771396</v>
+        <v>0.001973721701192037</v>
       </c>
       <c r="C4" t="n">
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.005287370676834787</v>
+        <v>0.007250892575701899</v>
       </c>
       <c r="E4" t="n">
-        <v>0.004625717825513074</v>
+        <v>0.005714207600577662</v>
       </c>
       <c r="F4" t="n">
-        <v>0.003229817566568383</v>
+        <v>0.002272958825079848</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003807527509224679</v>
+        <v>0.004940098549817994</v>
       </c>
       <c r="H4" t="n">
-        <v>0.00731753191137511</v>
+        <v>0.004413599075680328</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0003645638840972555</v>
+        <v>0.0003145110378811083</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00295762226336506</v>
+        <v>0.004549778277135114</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0144229934813679</v>
+        <v>0.01370317809576224</v>
       </c>
       <c r="L4" t="n">
-        <v>0.009581585134028013</v>
+        <v>0.01233423117503389</v>
       </c>
       <c r="M4" t="n">
-        <v>0.004274285021344512</v>
+        <v>0.005880430109306159</v>
       </c>
       <c r="N4" t="n">
-        <v>0.005687683968533773</v>
+        <v>0.007516785265013118</v>
       </c>
       <c r="O4" t="n">
-        <v>0.007654155254704123</v>
+        <v>0.01298304994167661</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01384674768510505</v>
+        <v>0.01231460135055075</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.0107062556805727</v>
+        <v>0.01264294681095081</v>
       </c>
       <c r="R4" t="n">
-        <v>0.00506546835542959</v>
+        <v>0.004061418796275765</v>
       </c>
       <c r="S4" t="n">
-        <v>0.003686677742654648</v>
+        <v>0.005333967270219325</v>
       </c>
       <c r="T4" t="n">
-        <v>0.004369698731787101</v>
+        <v>0.00379005224954805</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001879947589258195</v>
+        <v>0.00276489792779384</v>
       </c>
       <c r="V4" t="n">
-        <v>0.00038765813450832</v>
+        <v>0.0002954273904290948</v>
       </c>
       <c r="W4" t="n">
-        <v>0.01066044744788272</v>
+        <v>0.009608947397364355</v>
       </c>
       <c r="X4" t="n">
-        <v>0.002953293520478514</v>
+        <v>0.004261026844373776</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.00182971677143958</v>
+        <v>0.001562801534343278</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.002419925100233449</v>
+        <v>0.00145371418833763</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.00330843198879622</v>
+        <v>0.002390168740001993</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0008157679339702641</v>
+        <v>0.0007532184322991176</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.003687369849349281</v>
+        <v>0.005773547813897988</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.01090058623954977</v>
+        <v>0.007788549887242962</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.005375866164015549</v>
+        <v>0.003612371502313999</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.005154766179570652</v>
+        <v>0.006493123802156349</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0007103129447088187</v>
+        <v>0.0008691954822126368</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.001081989612013098</v>
+        <v>0.0006066350227163519</v>
       </c>
       <c r="AI4" t="n">
         <v>0</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.005282172212808549</v>
+        <v>0.005597680959253232</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.005926716942113811</v>
+        <v>0.008277926851144181</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.001673801659572025</v>
+        <v>0.001529607888252733</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.000996825468144241</v>
+        <v>0.0009095579834416691</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.00366891786806053</v>
+        <v>0.003614935053796717</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004134139113098654</v>
+        <v>0.003052270117098576</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001309220660990268</v>
+        <v>0.001369020264719939</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.003586735075450889</v>
+        <v>0.002328158951719621</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.00406334404096112</v>
+        <v>0.003719466038067196</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.002034913046974568</v>
+        <v>0.003994823914338756</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.003232931898757635</v>
+        <v>0.007189733110125336</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.003724455368851374</v>
+        <v>0.006916467633606938</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.004157043059511633</v>
+        <v>0.00288972442629389</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002549996552674616</v>
+        <v>0.004847444918649022</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001289834218190234</v>
+        <v>0.0006211240296390089</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.001992560097433627</v>
+        <v>0.004989168263807154</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.004469093109591663</v>
+        <v>0.007676708415447616</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.005627406364989293</v>
+        <v>0.009837933932287175</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.006588162893465329</v>
+        <v>0.007775805757850845</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.001327213143681832</v>
+        <v>0.00133243703131038</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001006428605392848</v>
+        <v>0.001114629250818022</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001168916705190214</v>
+        <v>0.0005489075318472286</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.00609905772876893</v>
+        <v>0.01101597500865373</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.005751244320539024</v>
+        <v>0.00811775656111152</v>
       </c>
       <c r="BH4" t="n">
-        <v>1.395761422401173e-05</v>
+        <v>1.872278069963713e-05</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.0009664594290181407</v>
+        <v>0.0009654899964692354</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002512967769006005</v>
+        <v>0.004278918919252129</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.003788377040456987</v>
+        <v>0.003472357735766411</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.001274327518407653</v>
+        <v>0.001213309449685665</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.003669275658297657</v>
+        <v>0.003085641974317647</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.005685339510536897</v>
+        <v>0.009690304242669331</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.00435261960221979</v>
+        <v>0.003448158205192973</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.003202594596222543</v>
+        <v>0.002967561127910229</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.0002394100124339785</v>
+        <v>0.0003294966847521179</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.008025606196247361</v>
+        <v>0.003977148876250771</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.005549536638586021</v>
+        <v>0.001763849693672097</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.002779402476599126</v>
+        <v>0.002104481200056239</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.0122726578522062</v>
+        <v>0.009290330147547593</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.00530891610267742</v>
+        <v>0.003496382577298594</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.006975890373955638</v>
+        <v>0.007729018500062673</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.0001905452280012142</v>
+        <v>0.0003932322808211817</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.002246304470282539</v>
+        <v>0.0007476965558508243</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.001310483636617638</v>
+        <v>0.000941434118061155</v>
       </c>
       <c r="CA4" t="n">
-        <v>9.664662775573362e-06</v>
+        <v>0.000144699379864293</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.001479921687390367</v>
+        <v>0.001571931976923519</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002175423165523008</v>
+        <v>0.004299180102839238</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001427425794181533</v>
+        <v>0.0002730086312952302</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.000804192576402433</v>
+        <v>0.001092159313102629</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.003894893175794856</v>
+        <v>0.00229442588168145</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004791596564349939</v>
+        <v>0.002379626105617204</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.002661410795452939</v>
+        <v>0.0007329115449496566</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.005226150523268358</v>
+        <v>0.002442882038317058</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.008421464894109471</v>
+        <v>0.006700862790709934</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002125183071628782</v>
+        <v>0.001478904694993559</v>
       </c>
     </row>
     <row r="5">
@@ -1690,268 +1690,268 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.007956318252730099</v>
+        <v>-0.004617784711388429</v>
       </c>
       <c r="C5" t="n">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.005474992601361373</v>
+        <v>-0.01136228435455084</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.004971885173128165</v>
+        <v>-0.01092043681747267</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.004203670811130811</v>
+        <v>-0.002772043644942446</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.005897965202005351</v>
+        <v>-0.007637864936596827</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.009342764515178303</v>
+        <v>-0.005421497963020971</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.000501031535514318</v>
+        <v>-0.0002368265245707657</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.00479431784551645</v>
+        <v>-0.006583463338533491</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.005108116577875276</v>
+        <v>-0.003572457505041748</v>
       </c>
       <c r="L5" t="n">
-        <v>0.008348134991119038</v>
+        <v>-0.003404381290704561</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.01013852048334808</v>
+        <v>-0.009132814750792273</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0106021319504465</v>
+        <v>-0.01037165082108903</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.004135893648449107</v>
+        <v>-0.01097666378565255</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.01087149187592324</v>
+        <v>-0.01787296898079765</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.007225007372456549</v>
+        <v>-0.01300501327042165</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.009932213380489241</v>
+        <v>-0.007013909440662913</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.007282415630550576</v>
+        <v>-0.005647425897035841</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.01068679692125516</v>
+        <v>-0.008111308466548273</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.004747861987614311</v>
+        <v>-0.007346585998271382</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.0007207771858351753</v>
+        <v>-0.0004736530491415203</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.01579722959033304</v>
+        <v>-0.01175950486295317</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.005599764220453884</v>
+        <v>-0.006864274570982809</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0008862629246676468</v>
+        <v>-0.001797819039198367</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.002722699023379738</v>
+        <v>-0.001242971293282047</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.003448275862068961</v>
+        <v>-0.001418020679468235</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001635930993456258</v>
+        <v>-0.001130279595478878</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.001509769094138524</v>
+        <v>-0.005445398046759409</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.03238602723505031</v>
+        <v>-0.01571936056838367</v>
       </c>
       <c r="AE5" t="n">
-        <v>-0.01208370173887414</v>
+        <v>-0.007854523227383892</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.01329173166926674</v>
+        <v>-0.01163929703255545</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001414677276746257</v>
+        <v>-0.002047677261613723</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001635930993456258</v>
+        <v>-0.0006778661951075904</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.01279251170046798</v>
+        <v>-0.01456797404895304</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.01746595618709291</v>
+        <v>-0.02238010657193605</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002592912705272199</v>
+        <v>-0.001356531996461174</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.002829354553492502</v>
+        <v>-0.001344743276283644</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.002574726250369974</v>
+        <v>-0.006333234684818001</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.008910597986974512</v>
+        <v>-0.004980842911877425</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.001326259946949604</v>
+        <v>-0.00336779911373708</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.004381290704558882</v>
+        <v>-0.002900266350991443</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.008227661456797441</v>
+        <v>-0.009177027827116657</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.003588143525741016</v>
+        <v>-0.004187041564792193</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.005829863176680517</v>
+        <v>-0.01901469317199652</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.002130807931340684</v>
+        <v>-0.002047677261613712</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.008812260536398464</v>
+        <v>-0.003140305387496378</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.004119850187265861</v>
+        <v>-0.01025641025641025</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.002858826996758057</v>
+        <v>-0.001356531996461174</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.002632403635224079</v>
+        <v>-0.008905927455027962</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.009680207433016364</v>
+        <v>-0.01872659176029961</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.01480389265703336</v>
+        <v>-0.01751656583117256</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.01136228435455084</v>
+        <v>-0.01029641185647421</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.003093396787626401</v>
+        <v>-0.001338488994646025</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.002052349791790586</v>
+        <v>-0.001864456939923043</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.002545885139135551</v>
+        <v>-0.0004439183190292906</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.01212906943244016</v>
+        <v>-0.01610486891385767</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.005647425897035841</v>
+        <v>-0.01722846441947564</v>
       </c>
       <c r="BH5" t="n">
-        <v>-2.947244326554355e-05</v>
+        <v>0</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001621940430551527</v>
+        <v>-0.002169926650366783</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.001635930993456247</v>
+        <v>-0.00651725154821583</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.01109458655562164</v>
+        <v>-0.006136560069144315</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.002201070791195692</v>
+        <v>-0.001479727730097646</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.001190849263553762</v>
+        <v>-0.004293324976496382</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.01170746092598057</v>
+        <v>-0.022241428983002</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.009890795631825244</v>
+        <v>-0.0003249630723781372</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.00542292956086059</v>
+        <v>-0.002511078286558344</v>
       </c>
       <c r="BQ5" t="n">
-        <v>-0.0003432137285491299</v>
+        <v>-0.0006240249609984261</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.01556145004420866</v>
+        <v>-0.007962253022707099</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.00792808723843207</v>
+        <v>-0.002534630120837045</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.001190849263553762</v>
+        <v>-0.005570291777188363</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.02272325375773653</v>
+        <v>-0.00347853337511751</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.008200118413262259</v>
+        <v>-0.004402141582391406</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.009777499216546559</v>
+        <v>-0.00567220307113755</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.0003667481662591898</v>
+        <v>-0.000503107428233196</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.00480400825228412</v>
+        <v>-0.0005897965202004806</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.003035661656351318</v>
+        <v>-0.001479727730097646</v>
       </c>
       <c r="CA5" t="n">
-        <v>0</v>
+        <v>-0.0004128575641403565</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.003006189213085786</v>
+        <v>-0.001886236368995042</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.001974653698791629</v>
+        <v>-0.004588513913558334</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.004509283819628673</v>
+        <v>-0.0008547008547008849</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.0015042306486995</v>
+        <v>-0.001296787503684094</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.005629236663719417</v>
+        <v>-0.0007104795737122638</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.003625110521662256</v>
+        <v>-0.002392909896602657</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.001355732390215158</v>
+        <v>-0.000908806016922592</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.01447096964338345</v>
+        <v>-0.002097488921713442</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.01732979664014146</v>
+        <v>-0.009088217880402616</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.003447195236602973</v>
+        <v>-0.001746595618709301</v>
       </c>
     </row>
     <row r="6">
@@ -1961,268 +1961,268 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.003946950595447848</v>
+        <v>-0.003103122139135064</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.003630480771149699</v>
+        <v>-0.004859031160496033</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.003535044772577376</v>
+        <v>-0.001565285281452078</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.001552523531072619</v>
+        <v>2.974105625678792e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.004692183087167792</v>
+        <v>-0.003826471037367146</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.00417839808716722</v>
+        <v>-0.004049019007370216</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.000294242670001979</v>
+        <v>5.883100742065675e-07</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.002689721205499301</v>
+        <v>-0.002939783400507337</v>
       </c>
       <c r="K6" t="n">
-        <v>0.004372793677354913</v>
+        <v>0.002226784966102507</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01279076432836415</v>
+        <v>0.00782998057622088</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.006555053854019138</v>
+        <v>-0.006007682912318901</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.003361945999257984</v>
+        <v>-0.004416426745879756</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.001771761805291983</v>
+        <v>-0.004112779449614484</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.006825389688533528</v>
+        <v>-0.00345713415260103</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.005240897527051827</v>
+        <v>0.00602808158929844</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.00481641584095586</v>
+        <v>-0.002701941785536571</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.003618780979674624</v>
+        <v>-0.002867287082566383</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.00172866454888079</v>
+        <v>-0.00314500713322543</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.002983090023892987</v>
+        <v>-0.001590329119413658</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.0003583864970641226</v>
+        <v>-0.0003185575698890331</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.0001508485812361598</v>
+        <v>-0.005302821393721468</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.00316495532130342</v>
+        <v>-0.004542880267448281</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0007483741840727254</v>
+        <v>-0.0006659955070482726</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.0006865196321294481</v>
+        <v>0.0003824304086972458</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.001389765180051539</v>
+        <v>0.001380128739785458</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0001780257677797603</v>
+        <v>-0.0003209046454767939</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.002009212728847631</v>
+        <v>0.003395018401895908</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.008619609777005552</v>
+        <v>-0.007135384381401888</v>
       </c>
       <c r="AE6" t="n">
-        <v>-0.008566846435806824</v>
+        <v>-0.003361544151986076</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.003257888096903488</v>
+        <v>-0.008551726176626509</v>
       </c>
       <c r="AG6" t="n">
-        <v>-0.0003801539847630847</v>
+        <v>-0.0003199839055924858</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0005027756570959024</v>
+        <v>-0.0002972176978110836</v>
       </c>
       <c r="AI6" t="n">
         <v>0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.008492101339990154</v>
+        <v>-0.003571215036865552</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.005962088409681191</v>
+        <v>-0.005571601159534381</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0007035066642324423</v>
+        <v>-0.0006351040292918691</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0003253958435606525</v>
+        <v>-1.46682824789357e-05</v>
       </c>
       <c r="AN6" t="n">
-        <v>0.000382477189523453</v>
+        <v>-0.0008532412197521683</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.003555721897988409</v>
+        <v>-0.004467057466946517</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0003193979379467721</v>
+        <v>-0.0007931667204891746</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.0008131481113693995</v>
+        <v>7.991982270977026e-05</v>
       </c>
       <c r="AR6" t="n">
-        <v>-0.00488580919106949</v>
+        <v>-0.006151334811189399</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.003083224414798386</v>
+        <v>-0.0006380276525448009</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.002868016438337972</v>
+        <v>-0.009925778708721194</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.001014646461357174</v>
+        <v>5.463373085575493e-05</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001805006414780491</v>
+        <v>-0.002398583247265948</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.001646711052109503</v>
+        <v>-0.002475681239963509</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0001558189006165584</v>
+        <v>-0.0001627961300288333</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0.0003068222614038135</v>
+        <v>-0.00219116834091771</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.003670373122469767</v>
+        <v>-0.0002125853097525083</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0.006242986500223283</v>
+        <v>-0.008491500397672042</v>
       </c>
       <c r="BB6" t="n">
-        <v>-0.004539375808814863</v>
+        <v>-0.004984808993097741</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.001034468852904791</v>
+        <v>-0.001028270578164714</v>
       </c>
       <c r="BD6" t="n">
-        <v>-0.000869772500699953</v>
+        <v>-0.0004532468374114001</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0004921512968259073</v>
+        <v>-0.0003517442536969256</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.007865232788952976</v>
+        <v>-0.009683931818129413</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.002617050470780233</v>
+        <v>-0.001885865999179043</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>-0.0006206602265973026</v>
+        <v>-0.001009887478887539</v>
       </c>
       <c r="BJ6" t="n">
-        <v>-0.0007820472643412125</v>
+        <v>-0.001121187057895989</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.00371777618519808</v>
+        <v>-0.003048020886862038</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.000479954541237193</v>
+        <v>-0.00108348924273354</v>
       </c>
       <c r="BM6" t="n">
-        <v>-0.0009340701804448903</v>
+        <v>-0.001075530484353773</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.008084142169767867</v>
+        <v>-0.008942956276696655</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.003763851040205421</v>
+        <v>0.0001251472183613322</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.000592374988332256</v>
+        <v>-1.319058385299832e-05</v>
       </c>
       <c r="BQ6" t="n">
-        <v>-0.0002077338250900562</v>
+        <v>-0.0002085907234481016</v>
       </c>
       <c r="BR6" t="n">
-        <v>-0.004736563423563938</v>
+        <v>-0.0009091348304360008</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.002378595361802282</v>
+        <v>-0.001730648235610841</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0.0006060017104733112</v>
+        <v>-0.00103604595724191</v>
       </c>
       <c r="BU6" t="n">
-        <v>-0.001893244863539412</v>
+        <v>-0.002142025010677207</v>
       </c>
       <c r="BV6" t="n">
-        <v>-0.0019811818629899</v>
+        <v>-0.002767298649658906</v>
       </c>
       <c r="BW6" t="n">
-        <v>-0.001215454549385076</v>
+        <v>-0.001583177528421925</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.000245740864117322</v>
+        <v>-0.0002603892050060536</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.001173365266318077</v>
+        <v>-3.701290543357827e-05</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0003209046454767883</v>
+        <v>-0.000185161018613067</v>
       </c>
       <c r="CA6" t="n">
         <v>0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.0005856394080269555</v>
+        <v>-2.218934522442151e-05</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.001035738527696575</v>
+        <v>0.001230886684225108</v>
       </c>
       <c r="CD6" t="n">
-        <v>0</v>
+        <v>-0.0001220096308488405</v>
       </c>
       <c r="CE6" t="n">
-        <v>-7.307055148181306e-06</v>
+        <v>-0.0004662264689400536</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.002367460274108949</v>
+        <v>0.001469592555368554</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.002009156568950662</v>
+        <v>0.0001396053948839598</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0006170466991210654</v>
+        <v>-0.0004055232059802183</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0009905619024841161</v>
+        <v>4.677088626098559e-05</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-0.002474688872154418</v>
+        <v>-0.002613346490491947</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.001790419020283288</v>
+        <v>-0.0004160145935501125</v>
       </c>
     </row>
     <row r="7">
@@ -2232,268 +2232,268 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0007082544733961859</v>
+        <v>-0.001203731691838239</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.001450926479553683</v>
+        <v>0.001057350900569215</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.001334042742019831</v>
+        <v>0.002616230143326021</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0002398217164708838</v>
+        <v>0.002538643232485899</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.002208060897844299</v>
+        <v>-0.001893908188618165</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.001245891914927455</v>
+        <v>-0.0001121235750778937</v>
       </c>
       <c r="I7" t="n">
-        <v>1.479727730097635e-05</v>
+        <v>0.0001184680517821113</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.001224186035982516</v>
+        <v>-0.001858447140054026</v>
       </c>
       <c r="K7" t="n">
-        <v>0.01041903791066068</v>
+        <v>0.01234295323929226</v>
       </c>
       <c r="L7" t="n">
-        <v>0.02020524393990977</v>
+        <v>0.0144424093027444</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.001515337374795378</v>
+        <v>3.082767721978587e-05</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.0009732474323936091</v>
+        <v>-0.001012363772073138</v>
       </c>
       <c r="O7" t="n">
-        <v>0.001653707711363539</v>
+        <v>0.0003222411499758159</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0026774524121219</v>
+        <v>0.005271549746535753</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.01065783268011159</v>
+        <v>0.009432385531629395</v>
       </c>
       <c r="R7" t="n">
-        <v>-0.002675326932998401</v>
+        <v>-0.00127722396415762</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.000931074413474875</v>
+        <v>-0.001616515615604624</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0001352896757555844</v>
+        <v>1.935585172591075e-06</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.001243150893154549</v>
+        <v>-0.001222551579041142</v>
       </c>
       <c r="V7" t="n">
-        <v>2.927717052537693e-05</v>
+        <v>1.477104874445523e-05</v>
       </c>
       <c r="W7" t="n">
-        <v>0.001448795519113388</v>
+        <v>0.0004186634775203758</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.001361079117375175</v>
+        <v>-0.0033527129854232</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.001899887660408728</v>
+        <v>0.0007189976097947471</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.0003023670638462539</v>
+        <v>0.001935743450660132</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.001443552286473632</v>
+        <v>0.001848522090280763</v>
       </c>
       <c r="AB7" t="n">
-        <v>-1.479718448392786e-05</v>
+        <v>0.0002166729080635255</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.003900690012930585</v>
+        <v>0.004594021232107992</v>
       </c>
       <c r="AD7" t="n">
-        <v>-0.001167466342194262</v>
+        <v>-0.002074495739741777</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0.002899214069515615</v>
+        <v>-0.001162521112897013</v>
       </c>
       <c r="AF7" t="n">
-        <v>-0.002085888022466964</v>
+        <v>-0.00191963677207278</v>
       </c>
       <c r="AG7" t="n">
-        <v>-2.974419988098775e-05</v>
+        <v>0.0001627570175599724</v>
       </c>
       <c r="AH7" t="n">
-        <v>-0.0001479990559179134</v>
+        <v>0.0002124309691488913</v>
       </c>
       <c r="AI7" t="n">
         <v>0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.002183240120751934</v>
+        <v>-0.0003726168662622043</v>
       </c>
       <c r="AK7" t="n">
-        <v>-0.0008271813285677665</v>
+        <v>-0.001402882430932573</v>
       </c>
       <c r="AL7" t="n">
-        <v>-1.387302823164238e-05</v>
+        <v>0.0001241888670688196</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0002416216826553408</v>
+        <v>0.0004579283171159965</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.002938918799009865</v>
+        <v>0.001777020789962336</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0003810702461853499</v>
+        <v>-0.001312732171725572</v>
       </c>
       <c r="AP7" t="n">
-        <v>8.505541851904776e-05</v>
+        <v>-8.06377082669452e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.00140846786099203</v>
+        <v>0.001598174455088158</v>
       </c>
       <c r="AR7" t="n">
-        <v>-0.001312220267550584</v>
+        <v>-0.005191922619433515</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.001734188705586781</v>
+        <v>7.37503294962416e-05</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.0009375975837905503</v>
+        <v>-0.001322269365562612</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.002764702497677546</v>
+        <v>0.002626763781266528</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0002266891333401966</v>
+        <v>-0.000828216294668277</v>
       </c>
       <c r="AW7" t="n">
-        <v>-8.841720655121121e-05</v>
+        <v>-0.0005475737283759496</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0002549536057981471</v>
+        <v>0.0001775804690658022</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001070699007735648</v>
+        <v>0.0003117505615120308</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.0005270786561400009</v>
+        <v>0.000869164456386251</v>
       </c>
       <c r="BA7" t="n">
-        <v>-0.004228137810889127</v>
+        <v>-0.002086827864999074</v>
       </c>
       <c r="BB7" t="n">
-        <v>-0.003424557227904146</v>
+        <v>-0.002608786093492105</v>
       </c>
       <c r="BC7" t="n">
-        <v>-0.000465672472581341</v>
+        <v>-0.0002654258168347134</v>
       </c>
       <c r="BD7" t="n">
-        <v>-0.0006734840607406422</v>
+        <v>-0.0001984861003635541</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.426092389477107e-05</v>
+        <v>1.477104874446633e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0001465989242880494</v>
+        <v>0.001005412622378965</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0002551661517070647</v>
+        <v>0.003237539046966953</v>
       </c>
       <c r="BH7" t="n">
         <v>0</v>
       </c>
       <c r="BI7" t="n">
-        <v>-2.113264644887451e-07</v>
+        <v>-0.0001492262553853596</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0007076423346793148</v>
+        <v>-0.0003249630723781094</v>
       </c>
       <c r="BK7" t="n">
-        <v>-0.002978042152336241</v>
+        <v>-0.0006784587821660082</v>
       </c>
       <c r="BL7" t="n">
-        <v>-0.0001708081791775507</v>
+        <v>0.0003317813361285005</v>
       </c>
       <c r="BM7" t="n">
-        <v>-0.000413747757171784</v>
+        <v>0.002329958488814387</v>
       </c>
       <c r="BN7" t="n">
-        <v>-0.002361222049122741</v>
+        <v>-0.001967067424438812</v>
       </c>
       <c r="BO7" t="n">
-        <v>-0.001196165057919885</v>
+        <v>0.002237418877273756</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0005786982321313083</v>
+        <v>0.001900728975120109</v>
       </c>
       <c r="BQ7" t="n">
-        <v>-8.744995076958029e-05</v>
+        <v>-5.912805353571194e-05</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0005430030733893421</v>
+        <v>0.0002051355318614778</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0.0004152061839817033</v>
+        <v>-0.0004869344837175494</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0.0004431336274295594</v>
+        <v>0.0002675380279613115</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.003794789323364372</v>
+        <v>0.004517700344276387</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0003787517237133387</v>
+        <v>-0.0005923184817164973</v>
       </c>
       <c r="BW7" t="n">
-        <v>0.0005333314681915224</v>
+        <v>0.001491075951064858</v>
       </c>
       <c r="BX7" t="n">
-        <v>-8.722359791069612e-05</v>
+        <v>4.778299909814488e-05</v>
       </c>
       <c r="BY7" t="n">
-        <v>-4.824109982469739e-05</v>
+        <v>0.0005313550342613438</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0004126033664710038</v>
+        <v>0.0004764636599009386</v>
       </c>
       <c r="CA7" t="n">
         <v>0</v>
       </c>
       <c r="CB7" t="n">
-        <v>0.000320904645476755</v>
+        <v>0.0006774638605426986</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0004017828194790351</v>
+        <v>0.001909255787399638</v>
       </c>
       <c r="CD7" t="n">
         <v>0</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0002401831352299655</v>
+        <v>1.688995536148764e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.001177137919701809</v>
+        <v>0.002574287314180906</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.001314446806194119</v>
+        <v>0.001873989662123066</v>
       </c>
       <c r="CH7" t="n">
-        <v>-8.829924368810026e-05</v>
+        <v>-0.0001379955760526796</v>
       </c>
       <c r="CI7" t="n">
-        <v>-1.477537487749034e-05</v>
+        <v>0.001271740427840245</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.001836033685694216</v>
+        <v>0.0001729592695669632</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0.000693739955760142</v>
+        <v>-0.0001661573243628478</v>
       </c>
     </row>
     <row r="8">
@@ -2503,268 +2503,268 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00143661014840227</v>
+        <v>-0.0002284940033442789</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>0.001495956921987898</v>
+        <v>0.003856972004138648</v>
       </c>
       <c r="E8" t="n">
-        <v>0.002714704559507583</v>
+        <v>0.003811453208481367</v>
       </c>
       <c r="F8" t="n">
-        <v>0.001808682466882733</v>
+        <v>0.003300868608389035</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0002144813822791802</v>
+        <v>0.002234154510048494</v>
       </c>
       <c r="H8" t="n">
-        <v>0.005095292386013161</v>
+        <v>0.003093489282386647</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0002079550252961526</v>
+        <v>0.0002202146372114716</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0005578945281724285</v>
+        <v>-0.0007124492309933144</v>
       </c>
       <c r="K8" t="n">
-        <v>0.02668424887167642</v>
+        <v>0.02261157347544613</v>
       </c>
       <c r="L8" t="n">
-        <v>0.02159586912923277</v>
+        <v>0.02196357988462197</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0003928793693326466</v>
+        <v>0.00271195097127708</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0008804883749820996</v>
+        <v>0.001647992184706709</v>
       </c>
       <c r="O8" t="n">
-        <v>0.01125507453943853</v>
+        <v>0.01005664521779239</v>
       </c>
       <c r="P8" t="n">
-        <v>0.01866920795340998</v>
+        <v>0.01229589566950421</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01393017993581539</v>
+        <v>0.01257914503621709</v>
       </c>
       <c r="R8" t="n">
-        <v>0.000220716746947841</v>
+        <v>0.002144799376246404</v>
       </c>
       <c r="S8" t="n">
-        <v>-8.85829053202391e-06</v>
+        <v>0.0010767370881997</v>
       </c>
       <c r="T8" t="n">
-        <v>0.001612814433977106</v>
+        <v>0.0009877315060933785</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0002136578001193629</v>
+        <v>0.000523104043754241</v>
       </c>
       <c r="V8" t="n">
-        <v>0.0001920498622345057</v>
+        <v>0.0002170955860332002</v>
       </c>
       <c r="W8" t="n">
-        <v>0.007461487223533925</v>
+        <v>0.009013261752657539</v>
       </c>
       <c r="X8" t="n">
-        <v>0.001367382478143442</v>
+        <v>0.001573274062624166</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.002866360683098393</v>
+        <v>0.00202743656070328</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.002890228405164971</v>
+        <v>0.002503700081523913</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.002437057469396139</v>
+        <v>0.004380798198910249</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0005281850638328755</v>
+        <v>0.0007303838967741255</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.007657717527277549</v>
+        <v>0.008227546380731872</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.001494646044021428</v>
+        <v>0.001951393205263901</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.000269125852615032</v>
+        <v>0.001098526438676367</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.0007539931128107164</v>
+        <v>0.002509598134311611</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0002972570406458153</v>
+        <v>0.0004493559240991291</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0003816391946667608</v>
+        <v>0.0004662193666134379</v>
       </c>
       <c r="AI8" t="n">
         <v>0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.00113647203818196</v>
+        <v>0.002146975618913579</v>
       </c>
       <c r="AK8" t="n">
-        <v>-0.0001751383017690289</v>
+        <v>0.001874908867676911</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001161406646952096</v>
+        <v>0.001058917289991696</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.0002420492307000505</v>
+        <v>0.0007023718871682821</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.004966826259257266</v>
+        <v>0.003291821174626533</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.0007704893003844859</v>
+        <v>0.0003478516018140643</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001357029457272837</v>
+        <v>0.0004468216967882133</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.002871807240924773</v>
+        <v>0.002524438837279444</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.0006134846089844714</v>
+        <v>-0.001617321056683138</v>
       </c>
       <c r="AS8" t="n">
-        <v>-0.0011351062515911</v>
+        <v>0.004576027039901986</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.0002805187833621686</v>
+        <v>-4.435248906817235e-05</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.00452018348272479</v>
+        <v>0.005209220671687107</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.001890684062570328</v>
+        <v>0.002490427973803816</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.00220640604168206</v>
+        <v>0.0008721409490274473</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0006880934327865018</v>
+        <v>0.0004176816495902403</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.001945107565495954</v>
+        <v>0.001394051863924911</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002124091499109434</v>
+        <v>0.004424633446755486</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.001450285814666194</v>
+        <v>0.0002672265900657028</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.003641459080502995</v>
+        <v>0.002917909612375836</v>
       </c>
       <c r="BC8" t="n">
-        <v>-0.0002045360777895244</v>
+        <v>0.0006077578007606555</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.000656620160081106</v>
+        <v>0.0005733808031478466</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0001330839122064775</v>
+        <v>0.0001392071668657402</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.002735715142710754</v>
+        <v>0.003812263380399256</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.005082175401014711</v>
+        <v>0.006632875645099174</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.0003648576872170434</v>
+        <v>0.000177606751973966</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002477848891165876</v>
+        <v>0.0002122581249882072</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0007844528187630762</v>
+        <v>0.002580965460704515</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0003516824128990042</v>
+        <v>0.001020809338031381</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.001389174602248666</v>
+        <v>0.003476602693936998</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0001259566348671581</v>
+        <v>0.000276842867719021</v>
       </c>
       <c r="BO8" t="n">
-        <v>-1.176108275630083e-07</v>
+        <v>0.005788321417183715</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.002209127796728228</v>
+        <v>0.002845083789182121</v>
       </c>
       <c r="BQ8" t="n">
-        <v>-3.696696469592531e-05</v>
+        <v>6.024859136721794e-05</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.004610560621752644</v>
+        <v>0.001508314866174229</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.003259948687382197</v>
+        <v>0.0008334288815409763</v>
       </c>
       <c r="BT8" t="n">
-        <v>3.68100110336167e-05</v>
+        <v>0.001070573023101523</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.008390402499793389</v>
+        <v>0.00949219642555559</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.003282874806830236</v>
+        <v>0.001964066117938187</v>
       </c>
       <c r="BW8" t="n">
-        <v>0.005871927322066129</v>
+        <v>0.01013411904364419</v>
       </c>
       <c r="BX8" t="n">
-        <v>5.440584642234236e-05</v>
+        <v>0.0003476119788406645</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.0006360599812116008</v>
+        <v>0.0009552051977468612</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.001061357504865373</v>
+        <v>0.0007895589003203196</v>
       </c>
       <c r="CA8" t="n">
         <v>0</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001047472940172356</v>
+        <v>0.001844147383582367</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.002368103167773797</v>
+        <v>0.004504004514481639</v>
       </c>
       <c r="CD8" t="n">
         <v>0</v>
       </c>
       <c r="CE8" t="n">
-        <v>0.0008488499932722243</v>
+        <v>0.0003725945197335267</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.00362299907799804</v>
+        <v>0.003497203429400258</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.003463384229308925</v>
+        <v>0.003092278479955396</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.0002511602857688644</v>
+        <v>0.0006778487815517154</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.001087502663483697</v>
+        <v>0.004042002908881226</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0.00541372827204388</v>
+        <v>0.005027485293102996</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.001455875957476407</v>
+        <v>0.0009244507711342692</v>
       </c>
     </row>
     <row r="9">
@@ -2774,268 +2774,268 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005131229725744568</v>
+        <v>0.0007694584196507703</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0.01214264662540523</v>
+        <v>0.01111111111111108</v>
       </c>
       <c r="E9" t="n">
-        <v>0.008900677866195094</v>
+        <v>0.009460654288240467</v>
       </c>
       <c r="F9" t="n">
-        <v>0.007457098283931374</v>
+        <v>0.004461629982153481</v>
       </c>
       <c r="G9" t="n">
-        <v>0.006489859594383807</v>
+        <v>0.006867079280872346</v>
       </c>
       <c r="H9" t="n">
-        <v>0.01469578783151327</v>
+        <v>0.008030933967876264</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0006050129645635671</v>
+        <v>0.0008271787296898036</v>
       </c>
       <c r="J9" t="n">
-        <v>0.004648985959438401</v>
+        <v>0.008134394341290851</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0398762157382847</v>
+        <v>0.04002357795461242</v>
       </c>
       <c r="L9" t="n">
-        <v>0.03597758773223233</v>
+        <v>0.03740053050397875</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002545131695767933</v>
+        <v>0.009046454767726152</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01149425287356323</v>
+        <v>0.01756557618626581</v>
       </c>
       <c r="O9" t="n">
-        <v>0.01470674918950783</v>
+        <v>0.03418803418803416</v>
       </c>
       <c r="P9" t="n">
-        <v>0.02680187207488301</v>
+        <v>0.01951219512195123</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.03143961927424153</v>
+        <v>0.03310529446757884</v>
       </c>
       <c r="R9" t="n">
-        <v>0.008923556942277722</v>
+        <v>0.007346817370612746</v>
       </c>
       <c r="S9" t="n">
-        <v>0.006015924506045378</v>
+        <v>0.01288705396638166</v>
       </c>
       <c r="T9" t="n">
-        <v>0.005603066941905</v>
+        <v>0.003743000294724408</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0005304212168487088</v>
+        <v>0.003271441202475667</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0004420866489832087</v>
+        <v>0.0003255401006214798</v>
       </c>
       <c r="W9" t="n">
-        <v>0.01870415647921758</v>
+        <v>0.01849022004889974</v>
       </c>
       <c r="X9" t="n">
-        <v>0.003166617342408939</v>
+        <v>0.005860231902225022</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.005678627145085835</v>
+        <v>0.002624594514892409</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.0043055145974638</v>
+        <v>0.003369734789391621</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.007674003569304044</v>
+        <v>0.005681142177275433</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.001473622163277366</v>
+        <v>0.001440507058484608</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.0086943707633363</v>
+        <v>0.014414976599064</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.003169115528666133</v>
+        <v>0.009339678762641301</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.003758508434448005</v>
+        <v>0.003807257584770973</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.003574593796159509</v>
+        <v>0.005452836101535574</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.001210025929127112</v>
+        <v>0.001002654084340937</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.002218380870066328</v>
+        <v>0.00120908286641116</v>
       </c>
       <c r="AI9" t="n">
         <v>0</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.002012429712932784</v>
+        <v>0.004126142057176508</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.002409280190362906</v>
+        <v>0.008417608566329582</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.002933985330073319</v>
+        <v>0.003124078986147916</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0007372456502506508</v>
+        <v>0.00168092008257158</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.008286641108817406</v>
+        <v>0.004494382022471932</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.002747415066469705</v>
+        <v>0.00374776918500892</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.002535292422932922</v>
+        <v>0.0009088060169226031</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.006900619286346154</v>
+        <v>0.004600412857564184</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.003313166234514586</v>
+        <v>0.001509322284699588</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.00303390838786437</v>
+        <v>0.00952679410842997</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.005867970660146704</v>
+        <v>0.003541209652146671</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.009554703627248551</v>
+        <v>0.01945181255526079</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.00563255676791502</v>
+        <v>0.004756277695716371</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.003619344773790978</v>
+        <v>0.007614515169541969</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.001934477379095168</v>
+        <v>0.000749063670411998</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.003807257584770962</v>
+        <v>0.01075744179192452</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.003582001184132633</v>
+        <v>0.009875074360499702</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.004003667481662587</v>
+        <v>0.0191276156793398</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.008256880733944927</v>
+        <v>0.01688770999115824</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.002042024267534736</v>
+        <v>0.003088923556942313</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0009453471196454899</v>
+        <v>0.002036979003447215</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.001308744794765038</v>
+        <v>0.001128172986524623</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.004527966854098797</v>
+        <v>0.01918656056587088</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0104795737122558</v>
+        <v>0.0117074609259806</v>
       </c>
       <c r="BH9" t="n">
+        <v>5.92066311426942e-05</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>0.001154446177847157</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.006900654372397397</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.004418677530554705</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.001778471138845605</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.003937240970988742</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.01143530798703211</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.009519599174771543</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.008522559716897726</v>
+      </c>
+      <c r="BQ9" t="n">
+        <v>0.0006543723973824855</v>
+      </c>
+      <c r="BR9" t="n">
+        <v>0.007663497551138021</v>
+      </c>
+      <c r="BS9" t="n">
+        <v>0.002841077241787482</v>
+      </c>
+      <c r="BT9" t="n">
+        <v>0.00138288677614522</v>
+      </c>
+      <c r="BU9" t="n">
+        <v>0.02553818932468303</v>
+      </c>
+      <c r="BV9" t="n">
+        <v>0.006361642118458177</v>
+      </c>
+      <c r="BW9" t="n">
+        <v>0.01574756708935423</v>
+      </c>
+      <c r="BX9" t="n">
+        <v>0.0006189213085764589</v>
+      </c>
+      <c r="BY9" t="n">
+        <v>0.001840873634945461</v>
+      </c>
+      <c r="BZ9" t="n">
+        <v>0.001776198934280637</v>
+      </c>
+      <c r="CA9" t="n">
+        <v>0.0001566906925728473</v>
+      </c>
+      <c r="CB9" t="n">
+        <v>0.003658887928550869</v>
+      </c>
+      <c r="CC9" t="n">
+        <v>0.01223088923556948</v>
+      </c>
+      <c r="CD9" t="n">
         <v>2.974419988102106e-05</v>
       </c>
-      <c r="BI9" t="n">
-        <v>0.00189069423929098</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.005803432137285525</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.001558679706601429</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>0.002683307332293316</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>0.01082683307332295</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>0.004584352078239584</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>0.006050129645635294</v>
-      </c>
-      <c r="BP9" t="n">
-        <v>0.00596369922212624</v>
-      </c>
-      <c r="BQ9" t="n">
-        <v>0.0004278728606356474</v>
-      </c>
-      <c r="BR9" t="n">
-        <v>0.01233074042062809</v>
-      </c>
-      <c r="BS9" t="n">
-        <v>0.01091904350331321</v>
-      </c>
-      <c r="BT9" t="n">
-        <v>0.008153269951022802</v>
-      </c>
-      <c r="BU9" t="n">
-        <v>0.0251512532411409</v>
-      </c>
-      <c r="BV9" t="n">
-        <v>0.01025641025641032</v>
-      </c>
-      <c r="BW9" t="n">
-        <v>0.01642178046672433</v>
-      </c>
-      <c r="BX9" t="n">
-        <v>0.0001772525849335294</v>
-      </c>
-      <c r="BY9" t="n">
-        <v>0.003572457505041826</v>
-      </c>
-      <c r="BZ9" t="n">
-        <v>0.00144500147449127</v>
-      </c>
-      <c r="CA9" t="n">
-        <v>3.056234718825657e-05</v>
-      </c>
-      <c r="CB9" t="n">
-        <v>0.002093777646711847</v>
-      </c>
-      <c r="CC9" t="n">
-        <v>0.004069595989383612</v>
-      </c>
-      <c r="CD9" t="n">
-        <v>6.112469437651314e-05</v>
-      </c>
       <c r="CE9" t="n">
-        <v>0.001411696917314953</v>
+        <v>0.00273696341112073</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.005877268798617163</v>
+        <v>0.006894390473205891</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.01284932296168259</v>
+        <v>0.004656646035956336</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.007836358398156208</v>
+        <v>0.001069682151589191</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.005131229725744579</v>
+        <v>0.004656646035956347</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.01173695075199052</v>
+        <v>0.01351014040561627</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.003025064822817669</v>
+        <v>0.003572457505041793</v>
       </c>
     </row>
   </sheetData>
